--- a/artfynd/A 12205-2025 artfynd.xlsx
+++ b/artfynd/A 12205-2025 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125288182</v>
+        <v>125287628</v>
       </c>
       <c r="B2" t="n">
         <v>79891</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589211</v>
+        <v>589213</v>
       </c>
       <c r="R2" t="n">
-        <v>6931367</v>
+        <v>6931355</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125289297</v>
+        <v>125288613</v>
       </c>
       <c r="B3" t="n">
-        <v>57513</v>
+        <v>56112</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,27 +803,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589294</v>
+        <v>589274</v>
       </c>
       <c r="R3" t="n">
-        <v>6931466</v>
+        <v>6931451</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,12 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125288341</v>
+        <v>125289593</v>
       </c>
       <c r="B4" t="n">
-        <v>96979</v>
+        <v>91012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -921,25 +916,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589259</v>
+        <v>589278</v>
       </c>
       <c r="R4" t="n">
-        <v>6931398</v>
+        <v>6931421</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +979,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +989,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +1004,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125288594</v>
+        <v>125287933</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,39 +1032,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589268</v>
+        <v>589253</v>
       </c>
       <c r="R5" t="n">
-        <v>6931468</v>
+        <v>6931269</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1091,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1101,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1128,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125287933</v>
+        <v>125288954</v>
       </c>
       <c r="B6" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,34 +1144,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589253</v>
+        <v>589305</v>
       </c>
       <c r="R6" t="n">
-        <v>6931269</v>
+        <v>6931466</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1208,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1218,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1250,10 +1245,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125289593</v>
+        <v>125287248</v>
       </c>
       <c r="B7" t="n">
-        <v>91012</v>
+        <v>57513</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,34 +1261,53 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589278</v>
+        <v>589263</v>
       </c>
       <c r="R7" t="n">
-        <v>6931421</v>
+        <v>6931366</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1325,7 +1339,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1335,7 +1349,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Satt bakom ett träd, flög iväg när jag försökte få den på video.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1362,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125288954</v>
+        <v>125288594</v>
       </c>
       <c r="B8" t="n">
-        <v>57529</v>
+        <v>57666</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1378,27 +1397,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1407,10 +1426,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589305</v>
+        <v>589268</v>
       </c>
       <c r="R8" t="n">
-        <v>6931466</v>
+        <v>6931468</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1442,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1452,7 +1471,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,10 +1498,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125287248</v>
+        <v>125287941</v>
       </c>
       <c r="B9" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1495,41 +1514,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1538,10 +1543,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589263</v>
+        <v>589240</v>
       </c>
       <c r="R9" t="n">
-        <v>6931366</v>
+        <v>6931271</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1578,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,12 +1588,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Satt bakom ett träd, flög iväg när jag försökte få den på video.</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,12 +1603,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1732,10 +1732,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125287628</v>
+        <v>125288341</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>96979</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,25 +1744,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1772,10 +1772,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589213</v>
+        <v>589259</v>
       </c>
       <c r="R11" t="n">
-        <v>6931355</v>
+        <v>6931398</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1832,19 +1832,19 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125288613</v>
+        <v>125289100</v>
       </c>
       <c r="B12" t="n">
         <v>56112</v>
@@ -1877,7 +1877,11 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>äldre spillning</t>
@@ -1889,10 +1893,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589274</v>
+        <v>589290</v>
       </c>
       <c r="R12" t="n">
-        <v>6931451</v>
+        <v>6931449</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1924,7 +1928,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,7 +1938,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1961,10 +1965,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125287941</v>
+        <v>125288182</v>
       </c>
       <c r="B13" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1977,39 +1981,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589240</v>
+        <v>589211</v>
       </c>
       <c r="R13" t="n">
-        <v>6931271</v>
+        <v>6931367</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2041,7 +2040,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2051,7 +2050,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2078,10 +2077,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125289100</v>
+        <v>125289297</v>
       </c>
       <c r="B14" t="n">
-        <v>56112</v>
+        <v>57513</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2094,31 +2093,27 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2127,10 +2122,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589290</v>
+        <v>589294</v>
       </c>
       <c r="R14" t="n">
-        <v>6931449</v>
+        <v>6931466</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2162,7 +2157,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2172,7 +2167,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 12205-2025 artfynd.xlsx
+++ b/artfynd/A 12205-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125287628</v>
+        <v>125288594</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>57666</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589213</v>
+        <v>589268</v>
       </c>
       <c r="R2" t="n">
-        <v>6931355</v>
+        <v>6931468</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +780,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125288613</v>
+        <v>125289593</v>
       </c>
       <c r="B3" t="n">
-        <v>56112</v>
+        <v>91012</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,39 +808,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>206004</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589274</v>
+        <v>589278</v>
       </c>
       <c r="R3" t="n">
-        <v>6931451</v>
+        <v>6931421</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125289593</v>
+        <v>125288954</v>
       </c>
       <c r="B4" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,34 +920,39 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589278</v>
+        <v>589305</v>
       </c>
       <c r="R4" t="n">
-        <v>6931421</v>
+        <v>6931466</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -979,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -989,7 +994,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,22 +1009,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125287933</v>
+        <v>125288613</v>
       </c>
       <c r="B5" t="n">
-        <v>79891</v>
+        <v>56112</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1032,34 +1037,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589253</v>
+        <v>589274</v>
       </c>
       <c r="R5" t="n">
-        <v>6931269</v>
+        <v>6931451</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1091,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1101,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1116,22 +1126,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125288954</v>
+        <v>125288341</v>
       </c>
       <c r="B6" t="n">
-        <v>57529</v>
+        <v>96979</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1140,43 +1150,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589305</v>
+        <v>589259</v>
       </c>
       <c r="R6" t="n">
-        <v>6931466</v>
+        <v>6931398</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1208,7 +1213,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1218,7 +1223,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1250,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125287248</v>
+        <v>125289100</v>
       </c>
       <c r="B7" t="n">
-        <v>57513</v>
+        <v>56112</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1261,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>206004</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1283,19 +1288,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1304,10 +1299,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589263</v>
+        <v>589290</v>
       </c>
       <c r="R7" t="n">
-        <v>6931366</v>
+        <v>6931449</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1339,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1349,12 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Satt bakom ett träd, flög iväg när jag försökte få den på video.</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125288594</v>
+        <v>125288104</v>
       </c>
       <c r="B8" t="n">
-        <v>57666</v>
+        <v>56714</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,27 +1387,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1426,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589268</v>
+        <v>589218</v>
       </c>
       <c r="R8" t="n">
-        <v>6931468</v>
+        <v>6931404</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,7 +1461,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1486,22 +1476,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125287941</v>
+        <v>125287628</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1514,39 +1504,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589240</v>
+        <v>589213</v>
       </c>
       <c r="R9" t="n">
-        <v>6931271</v>
+        <v>6931355</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1578,7 +1563,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1588,7 +1573,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1603,22 +1588,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125288104</v>
+        <v>125287941</v>
       </c>
       <c r="B10" t="n">
-        <v>56714</v>
+        <v>57666</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1631,27 +1616,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1660,10 +1645,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589218</v>
+        <v>589240</v>
       </c>
       <c r="R10" t="n">
-        <v>6931404</v>
+        <v>6931271</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1695,7 +1680,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1705,7 +1690,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1720,22 +1705,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125288341</v>
+        <v>125289297</v>
       </c>
       <c r="B11" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1744,38 +1729,43 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589259</v>
+        <v>589294</v>
       </c>
       <c r="R11" t="n">
-        <v>6931398</v>
+        <v>6931466</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1807,7 +1797,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1817,7 +1807,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1832,22 +1827,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125289100</v>
+        <v>125287933</v>
       </c>
       <c r="B12" t="n">
-        <v>56112</v>
+        <v>79891</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1860,43 +1855,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589290</v>
+        <v>589253</v>
       </c>
       <c r="R12" t="n">
-        <v>6931449</v>
+        <v>6931269</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1928,7 +1914,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1938,7 +1924,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1953,12 +1939,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2077,7 +2063,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125289297</v>
+        <v>125287248</v>
       </c>
       <c r="B14" t="n">
         <v>57513</v>
@@ -2110,10 +2096,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2122,10 +2122,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589294</v>
+        <v>589263</v>
       </c>
       <c r="R14" t="n">
-        <v>6931466</v>
+        <v>6931366</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2157,7 +2157,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Satt bakom ett träd, flög iväg när jag försökte få den på video.</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 12205-2025 artfynd.xlsx
+++ b/artfynd/A 12205-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125288594</v>
+        <v>125287933</v>
       </c>
       <c r="B2" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,39 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589268</v>
+        <v>589253</v>
       </c>
       <c r="R2" t="n">
-        <v>6931468</v>
+        <v>6931269</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125289593</v>
+        <v>125288104</v>
       </c>
       <c r="B3" t="n">
-        <v>91012</v>
+        <v>56714</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,34 +803,39 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589278</v>
+        <v>589218</v>
       </c>
       <c r="R3" t="n">
-        <v>6931421</v>
+        <v>6931404</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +904,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125288954</v>
+        <v>125289297</v>
       </c>
       <c r="B4" t="n">
-        <v>57529</v>
+        <v>57513</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,16 +920,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589305</v>
+        <v>589294</v>
       </c>
       <c r="R4" t="n">
         <v>6931466</v>
@@ -984,7 +984,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,7 +994,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1009,22 +1014,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125288613</v>
+        <v>125289593</v>
       </c>
       <c r="B5" t="n">
-        <v>56112</v>
+        <v>91012</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1037,39 +1042,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>206004</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589274</v>
+        <v>589278</v>
       </c>
       <c r="R5" t="n">
-        <v>6931451</v>
+        <v>6931421</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1101,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1111,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,10 +1138,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125288341</v>
+        <v>125287248</v>
       </c>
       <c r="B6" t="n">
-        <v>96979</v>
+        <v>57513</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1150,38 +1150,57 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589259</v>
+        <v>589263</v>
       </c>
       <c r="R6" t="n">
-        <v>6931398</v>
+        <v>6931366</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1213,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1223,7 +1242,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Satt bakom ett träd, flög iväg när jag försökte få den på video.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,22 +1262,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125289100</v>
+        <v>125287941</v>
       </c>
       <c r="B7" t="n">
-        <v>56112</v>
+        <v>57666</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1266,31 +1290,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>206004</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1299,10 +1319,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589290</v>
+        <v>589240</v>
       </c>
       <c r="R7" t="n">
-        <v>6931449</v>
+        <v>6931271</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,7 +1354,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1364,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,22 +1379,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125288104</v>
+        <v>125287628</v>
       </c>
       <c r="B8" t="n">
-        <v>56714</v>
+        <v>79891</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1387,39 +1407,34 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589218</v>
+        <v>589213</v>
       </c>
       <c r="R8" t="n">
-        <v>6931404</v>
+        <v>6931355</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1451,7 +1466,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,7 +1476,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,10 +1503,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125287628</v>
+        <v>125289100</v>
       </c>
       <c r="B9" t="n">
-        <v>79891</v>
+        <v>56112</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1504,34 +1519,43 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589213</v>
+        <v>589290</v>
       </c>
       <c r="R9" t="n">
-        <v>6931355</v>
+        <v>6931449</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1563,7 +1587,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1573,7 +1597,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1600,10 +1624,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125287941</v>
+        <v>125288182</v>
       </c>
       <c r="B10" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1616,39 +1640,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589240</v>
+        <v>589211</v>
       </c>
       <c r="R10" t="n">
-        <v>6931271</v>
+        <v>6931367</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1680,7 +1699,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1690,7 +1709,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,10 +1736,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125289297</v>
+        <v>125288594</v>
       </c>
       <c r="B11" t="n">
-        <v>57513</v>
+        <v>57666</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1733,27 +1752,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1762,10 +1781,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589294</v>
+        <v>589268</v>
       </c>
       <c r="R11" t="n">
-        <v>6931466</v>
+        <v>6931468</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1797,7 +1816,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1807,12 +1826,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,22 +1841,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125287933</v>
+        <v>125288613</v>
       </c>
       <c r="B12" t="n">
-        <v>79891</v>
+        <v>56112</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1855,34 +1869,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589253</v>
+        <v>589274</v>
       </c>
       <c r="R12" t="n">
-        <v>6931269</v>
+        <v>6931451</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1914,7 +1933,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1924,7 +1943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1939,22 +1958,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125288182</v>
+        <v>125288954</v>
       </c>
       <c r="B13" t="n">
-        <v>79891</v>
+        <v>57529</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1967,34 +1986,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589211</v>
+        <v>589305</v>
       </c>
       <c r="R13" t="n">
-        <v>6931367</v>
+        <v>6931466</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2026,7 +2050,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2036,7 +2060,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2063,10 +2087,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125287248</v>
+        <v>125288341</v>
       </c>
       <c r="B14" t="n">
-        <v>57513</v>
+        <v>96979</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2075,57 +2099,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589263</v>
+        <v>589259</v>
       </c>
       <c r="R14" t="n">
-        <v>6931366</v>
+        <v>6931398</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2157,7 +2162,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2167,12 +2172,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Satt bakom ett träd, flög iväg när jag försökte få den på video.</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2187,12 +2187,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 12205-2025 artfynd.xlsx
+++ b/artfynd/A 12205-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125287933</v>
+        <v>125288341</v>
       </c>
       <c r="B2" t="n">
-        <v>79891</v>
+        <v>96979</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589253</v>
+        <v>589259</v>
       </c>
       <c r="R2" t="n">
-        <v>6931269</v>
+        <v>6931398</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125288104</v>
+        <v>125288613</v>
       </c>
       <c r="B3" t="n">
-        <v>56714</v>
+        <v>56112</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102612</v>
+        <v>206004</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589218</v>
+        <v>589274</v>
       </c>
       <c r="R3" t="n">
-        <v>6931404</v>
+        <v>6931451</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +867,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +877,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,7 +904,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125289297</v>
+        <v>125287248</v>
       </c>
       <c r="B4" t="n">
         <v>57513</v>
@@ -937,10 +937,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -949,10 +963,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589294</v>
+        <v>589263</v>
       </c>
       <c r="R4" t="n">
-        <v>6931466</v>
+        <v>6931366</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -984,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -994,12 +1008,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>Satt bakom ett träd, flög iväg när jag försökte få den på video.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,10 +1040,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125289593</v>
+        <v>125288954</v>
       </c>
       <c r="B5" t="n">
-        <v>91012</v>
+        <v>57529</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1042,34 +1056,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589278</v>
+        <v>589305</v>
       </c>
       <c r="R5" t="n">
-        <v>6931421</v>
+        <v>6931466</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1101,7 +1120,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1111,7 +1130,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,22 +1145,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125287248</v>
+        <v>125289593</v>
       </c>
       <c r="B6" t="n">
-        <v>57513</v>
+        <v>91012</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,53 +1173,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589263</v>
+        <v>589278</v>
       </c>
       <c r="R6" t="n">
-        <v>6931366</v>
+        <v>6931421</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,12 +1242,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Satt bakom ett träd, flög iväg när jag försökte få den på video.</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1274,10 +1269,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125287941</v>
+        <v>125287933</v>
       </c>
       <c r="B7" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1290,39 +1285,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589240</v>
+        <v>589253</v>
       </c>
       <c r="R7" t="n">
-        <v>6931271</v>
+        <v>6931269</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1391,10 +1381,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125287628</v>
+        <v>125289297</v>
       </c>
       <c r="B8" t="n">
-        <v>79891</v>
+        <v>57513</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1407,34 +1397,39 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589213</v>
+        <v>589294</v>
       </c>
       <c r="R8" t="n">
-        <v>6931355</v>
+        <v>6931466</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1466,7 +1461,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1476,7 +1471,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,10 +1503,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125289100</v>
+        <v>125287941</v>
       </c>
       <c r="B9" t="n">
-        <v>56112</v>
+        <v>57666</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1519,31 +1519,27 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>206004</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1552,10 +1548,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589290</v>
+        <v>589240</v>
       </c>
       <c r="R9" t="n">
-        <v>6931449</v>
+        <v>6931271</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1587,7 +1583,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1597,7 +1593,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1612,12 +1608,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1736,10 +1732,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125288594</v>
+        <v>125287628</v>
       </c>
       <c r="B11" t="n">
-        <v>57666</v>
+        <v>79891</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1752,39 +1748,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589268</v>
+        <v>589213</v>
       </c>
       <c r="R11" t="n">
-        <v>6931468</v>
+        <v>6931355</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1816,7 +1807,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1826,7 +1817,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1841,22 +1832,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125288613</v>
+        <v>125288104</v>
       </c>
       <c r="B12" t="n">
-        <v>56112</v>
+        <v>56714</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1869,21 +1860,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>206004</v>
+        <v>102612</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1898,10 +1889,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589274</v>
+        <v>589218</v>
       </c>
       <c r="R12" t="n">
-        <v>6931451</v>
+        <v>6931404</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1933,7 +1924,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1943,7 +1934,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1970,10 +1961,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125288954</v>
+        <v>125288594</v>
       </c>
       <c r="B13" t="n">
-        <v>57529</v>
+        <v>57666</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1986,27 +1977,27 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -2015,10 +2006,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589305</v>
+        <v>589268</v>
       </c>
       <c r="R13" t="n">
-        <v>6931466</v>
+        <v>6931468</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2050,7 +2041,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2060,7 +2051,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2087,10 +2078,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125288341</v>
+        <v>125289100</v>
       </c>
       <c r="B14" t="n">
-        <v>96979</v>
+        <v>56112</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2099,38 +2090,47 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>206004</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589259</v>
+        <v>589290</v>
       </c>
       <c r="R14" t="n">
-        <v>6931398</v>
+        <v>6931449</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2187,12 +2187,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 12205-2025 artfynd.xlsx
+++ b/artfynd/A 12205-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125288341</v>
+        <v>125287628</v>
       </c>
       <c r="B2" t="n">
-        <v>96979</v>
+        <v>80028</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589259</v>
+        <v>589213</v>
       </c>
       <c r="R2" t="n">
-        <v>6931398</v>
+        <v>6931355</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125288613</v>
+        <v>125289100</v>
       </c>
       <c r="B3" t="n">
-        <v>56112</v>
+        <v>56226</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,7 +820,11 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>äldre spillning</t>
@@ -832,10 +836,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589274</v>
+        <v>589290</v>
       </c>
       <c r="R3" t="n">
-        <v>6931451</v>
+        <v>6931449</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -867,7 +871,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -877,7 +881,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -904,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125287248</v>
+        <v>125287941</v>
       </c>
       <c r="B4" t="n">
-        <v>57513</v>
+        <v>57793</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -920,41 +924,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -963,10 +953,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589263</v>
+        <v>589240</v>
       </c>
       <c r="R4" t="n">
-        <v>6931366</v>
+        <v>6931271</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -998,7 +988,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,12 +998,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Satt bakom ett träd, flög iväg när jag försökte få den på video.</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1028,22 +1013,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125288954</v>
+        <v>125288613</v>
       </c>
       <c r="B5" t="n">
-        <v>57529</v>
+        <v>56226</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,27 +1041,27 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>206004</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1085,10 +1070,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589305</v>
+        <v>589274</v>
       </c>
       <c r="R5" t="n">
-        <v>6931466</v>
+        <v>6931451</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1120,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1130,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,22 +1130,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125289593</v>
+        <v>125288182</v>
       </c>
       <c r="B6" t="n">
-        <v>91012</v>
+        <v>80028</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1173,21 +1158,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1197,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589278</v>
+        <v>589211</v>
       </c>
       <c r="R6" t="n">
-        <v>6931421</v>
+        <v>6931367</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1232,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1242,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,22 +1242,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125287933</v>
+        <v>125289297</v>
       </c>
       <c r="B7" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,34 +1270,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589253</v>
+        <v>589294</v>
       </c>
       <c r="R7" t="n">
-        <v>6931269</v>
+        <v>6931466</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1344,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1344,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1369,22 +1364,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125289297</v>
+        <v>125288594</v>
       </c>
       <c r="B8" t="n">
-        <v>57513</v>
+        <v>57793</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,27 +1392,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1426,10 +1421,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589294</v>
+        <v>589268</v>
       </c>
       <c r="R8" t="n">
-        <v>6931466</v>
+        <v>6931468</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1461,7 +1456,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1471,12 +1466,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,22 +1481,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125287941</v>
+        <v>125287933</v>
       </c>
       <c r="B9" t="n">
-        <v>57666</v>
+        <v>80028</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1519,39 +1509,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589240</v>
+        <v>589253</v>
       </c>
       <c r="R9" t="n">
-        <v>6931271</v>
+        <v>6931269</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1620,10 +1605,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125288182</v>
+        <v>125288954</v>
       </c>
       <c r="B10" t="n">
-        <v>79891</v>
+        <v>57632</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1636,34 +1621,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589211</v>
+        <v>589305</v>
       </c>
       <c r="R10" t="n">
-        <v>6931367</v>
+        <v>6931466</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1695,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1705,7 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1732,10 +1722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125287628</v>
+        <v>125287248</v>
       </c>
       <c r="B11" t="n">
-        <v>79891</v>
+        <v>57635</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1748,34 +1738,53 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589213</v>
+        <v>589263</v>
       </c>
       <c r="R11" t="n">
-        <v>6931355</v>
+        <v>6931366</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1818,6 +1827,11 @@
       <c r="AB11" t="inlineStr">
         <is>
           <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Satt bakom ett träd, flög iväg när jag försökte få den på video.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1844,10 +1858,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125288104</v>
+        <v>125288341</v>
       </c>
       <c r="B12" t="n">
-        <v>56714</v>
+        <v>97147</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1856,43 +1870,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102612</v>
+        <v>221945</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589218</v>
+        <v>589259</v>
       </c>
       <c r="R12" t="n">
-        <v>6931404</v>
+        <v>6931398</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1924,7 +1933,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1934,7 +1943,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1949,22 +1958,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125288594</v>
+        <v>125289593</v>
       </c>
       <c r="B13" t="n">
-        <v>57666</v>
+        <v>91166</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1977,39 +1986,34 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589268</v>
+        <v>589278</v>
       </c>
       <c r="R13" t="n">
-        <v>6931468</v>
+        <v>6931421</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2041,7 +2045,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2051,7 +2055,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2066,22 +2070,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125289100</v>
+        <v>125288104</v>
       </c>
       <c r="B14" t="n">
-        <v>56112</v>
+        <v>56828</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2094,28 +2098,24 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>206004</v>
+        <v>102612</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>äldre spillning</t>
@@ -2127,10 +2127,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589290</v>
+        <v>589218</v>
       </c>
       <c r="R14" t="n">
-        <v>6931449</v>
+        <v>6931404</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 12205-2025 artfynd.xlsx
+++ b/artfynd/A 12205-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125287628</v>
+        <v>125288954</v>
       </c>
       <c r="B2" t="n">
-        <v>80028</v>
+        <v>57632</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,39 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589213</v>
+        <v>589305</v>
       </c>
       <c r="R2" t="n">
-        <v>6931355</v>
+        <v>6931466</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +755,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +765,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,19 +780,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125289100</v>
+        <v>125288613</v>
       </c>
       <c r="B3" t="n">
         <v>56226</v>
@@ -820,11 +825,7 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>äldre spillning</t>
@@ -836,10 +837,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589290</v>
+        <v>589274</v>
       </c>
       <c r="R3" t="n">
-        <v>6931449</v>
+        <v>6931451</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -871,7 +872,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -881,7 +882,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -908,7 +909,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125287941</v>
+        <v>125288594</v>
       </c>
       <c r="B4" t="n">
         <v>57793</v>
@@ -953,10 +954,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589240</v>
+        <v>589268</v>
       </c>
       <c r="R4" t="n">
-        <v>6931271</v>
+        <v>6931468</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +989,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -998,7 +999,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1025,7 +1026,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125288613</v>
+        <v>125289100</v>
       </c>
       <c r="B5" t="n">
         <v>56226</v>
@@ -1058,7 +1059,11 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>äldre spillning</t>
@@ -1070,10 +1075,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589274</v>
+        <v>589290</v>
       </c>
       <c r="R5" t="n">
-        <v>6931451</v>
+        <v>6931449</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,10 +1147,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125288182</v>
+        <v>125288341</v>
       </c>
       <c r="B6" t="n">
-        <v>80028</v>
+        <v>97147</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1154,25 +1159,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1182,10 +1187,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589211</v>
+        <v>589259</v>
       </c>
       <c r="R6" t="n">
-        <v>6931367</v>
+        <v>6931398</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1222,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1232,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,10 +1259,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125289297</v>
+        <v>125289593</v>
       </c>
       <c r="B7" t="n">
-        <v>57635</v>
+        <v>91166</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1270,39 +1275,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589294</v>
+        <v>589278</v>
       </c>
       <c r="R7" t="n">
-        <v>6931466</v>
+        <v>6931421</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,12 +1344,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,10 +1371,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125288594</v>
+        <v>125289297</v>
       </c>
       <c r="B8" t="n">
-        <v>57793</v>
+        <v>57635</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1392,27 +1387,27 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -1421,10 +1416,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589268</v>
+        <v>589294</v>
       </c>
       <c r="R8" t="n">
-        <v>6931468</v>
+        <v>6931466</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,7 +1451,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1466,7 +1461,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,22 +1481,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125287933</v>
+        <v>125288104</v>
       </c>
       <c r="B9" t="n">
-        <v>80028</v>
+        <v>56828</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1509,34 +1509,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589253</v>
+        <v>589218</v>
       </c>
       <c r="R9" t="n">
-        <v>6931269</v>
+        <v>6931404</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1568,7 +1573,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1578,7 +1583,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,22 +1598,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125288954</v>
+        <v>125288182</v>
       </c>
       <c r="B10" t="n">
-        <v>57632</v>
+        <v>80028</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1621,39 +1626,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589305</v>
+        <v>589211</v>
       </c>
       <c r="R10" t="n">
-        <v>6931466</v>
+        <v>6931367</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1695,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,10 +1722,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125287248</v>
+        <v>125287941</v>
       </c>
       <c r="B11" t="n">
-        <v>57635</v>
+        <v>57793</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,41 +1738,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1781,10 +1767,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589263</v>
+        <v>589240</v>
       </c>
       <c r="R11" t="n">
-        <v>6931366</v>
+        <v>6931271</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1816,7 +1802,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1826,12 +1812,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Satt bakom ett träd, flög iväg när jag försökte få den på video.</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1846,22 +1827,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125288341</v>
+        <v>125287248</v>
       </c>
       <c r="B12" t="n">
-        <v>97147</v>
+        <v>57635</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1870,38 +1851,57 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589259</v>
+        <v>589263</v>
       </c>
       <c r="R12" t="n">
-        <v>6931398</v>
+        <v>6931366</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1933,7 +1933,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1943,7 +1943,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Satt bakom ett träd, flög iväg när jag försökte få den på video.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1958,22 +1963,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125289593</v>
+        <v>125287933</v>
       </c>
       <c r="B13" t="n">
-        <v>91166</v>
+        <v>80028</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1986,21 +1991,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2010,10 +2015,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589278</v>
+        <v>589253</v>
       </c>
       <c r="R13" t="n">
-        <v>6931421</v>
+        <v>6931269</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2045,7 +2050,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2055,7 +2060,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2070,22 +2075,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125288104</v>
+        <v>125287628</v>
       </c>
       <c r="B14" t="n">
-        <v>56828</v>
+        <v>80028</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2098,39 +2103,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589218</v>
+        <v>589213</v>
       </c>
       <c r="R14" t="n">
-        <v>6931404</v>
+        <v>6931355</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2162,7 +2162,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2172,7 +2172,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 12205-2025 artfynd.xlsx
+++ b/artfynd/A 12205-2025 artfynd.xlsx
@@ -1610,10 +1610,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125288182</v>
+        <v>125287941</v>
       </c>
       <c r="B10" t="n">
-        <v>80028</v>
+        <v>57793</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1626,34 +1626,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589211</v>
+        <v>589240</v>
       </c>
       <c r="R10" t="n">
-        <v>6931367</v>
+        <v>6931271</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1685,7 +1690,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1695,7 +1700,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1722,10 +1727,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125287941</v>
+        <v>125288182</v>
       </c>
       <c r="B11" t="n">
-        <v>57793</v>
+        <v>80028</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1738,39 +1743,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589240</v>
+        <v>589211</v>
       </c>
       <c r="R11" t="n">
-        <v>6931271</v>
+        <v>6931367</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,7 +1802,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 12205-2025 artfynd.xlsx
+++ b/artfynd/A 12205-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125288954</v>
+        <v>125288594</v>
       </c>
       <c r="B2" t="n">
-        <v>57632</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,27 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -720,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589305</v>
+        <v>589268</v>
       </c>
       <c r="R2" t="n">
-        <v>6931466</v>
+        <v>6931468</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -755,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -765,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,15 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125288613</v>
+        <v>125287248</v>
       </c>
       <c r="B3" t="n">
-        <v>56226</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,27 +798,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>206004</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -837,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589274</v>
+        <v>589263</v>
       </c>
       <c r="R3" t="n">
-        <v>6931451</v>
+        <v>6931366</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -882,7 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Satt bakom ett träd, flög iväg när jag försökte få den på video.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -909,15 +918,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125288594</v>
+        <v>125289297</v>
       </c>
       <c r="B4" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,27 +929,27 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -954,10 +958,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589268</v>
+        <v>589294</v>
       </c>
       <c r="R4" t="n">
-        <v>6931468</v>
+        <v>6931466</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -989,7 +993,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -999,7 +1003,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,71 +1023,57 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125289100</v>
+        <v>125288341</v>
       </c>
       <c r="B5" t="n">
-        <v>56226</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97202</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>206004</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589290</v>
+        <v>589259</v>
       </c>
       <c r="R5" t="n">
-        <v>6931449</v>
+        <v>6931398</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1105,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1115,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1135,62 +1130,62 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125288341</v>
+        <v>125288104</v>
       </c>
       <c r="B6" t="n">
-        <v>97147</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56834</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589259</v>
+        <v>589218</v>
       </c>
       <c r="R6" t="n">
-        <v>6931398</v>
+        <v>6931404</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1222,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1232,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,27 +1242,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125289593</v>
+        <v>125287941</v>
       </c>
       <c r="B7" t="n">
-        <v>91166</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57811</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,34 +1265,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589278</v>
+        <v>589240</v>
       </c>
       <c r="R7" t="n">
-        <v>6931421</v>
+        <v>6931271</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1334,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1344,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1359,27 +1354,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125289297</v>
+        <v>125288954</v>
       </c>
       <c r="B8" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57648</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,16 +1377,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1416,7 +1406,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589294</v>
+        <v>589305</v>
       </c>
       <c r="R8" t="n">
         <v>6931466</v>
@@ -1451,7 +1441,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1461,12 +1451,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,27 +1466,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125288104</v>
+        <v>125287628</v>
       </c>
       <c r="B9" t="n">
-        <v>56828</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1509,39 +1489,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589218</v>
+        <v>589213</v>
       </c>
       <c r="R9" t="n">
-        <v>6931404</v>
+        <v>6931355</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1573,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1583,7 +1558,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1610,15 +1585,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125287941</v>
+        <v>125288613</v>
       </c>
       <c r="B10" t="n">
-        <v>57793</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56227</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1626,27 +1596,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>206004</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1655,10 +1625,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589240</v>
+        <v>589274</v>
       </c>
       <c r="R10" t="n">
-        <v>6931271</v>
+        <v>6931451</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1690,7 +1660,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1700,7 +1670,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1715,27 +1685,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125288182</v>
+        <v>125289100</v>
       </c>
       <c r="B11" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56227</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1743,34 +1708,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589211</v>
+        <v>589290</v>
       </c>
       <c r="R11" t="n">
-        <v>6931367</v>
+        <v>6931449</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1802,7 +1776,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1812,7 +1786,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1827,27 +1801,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125287248</v>
+        <v>125289593</v>
       </c>
       <c r="B12" t="n">
-        <v>57635</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91220</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1855,53 +1824,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589263</v>
+        <v>589278</v>
       </c>
       <c r="R12" t="n">
-        <v>6931366</v>
+        <v>6931421</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1933,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1943,12 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Satt bakom ett träd, flög iväg när jag försökte få den på video.</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1975,15 +1920,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125287933</v>
+        <v>125288182</v>
       </c>
       <c r="B13" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2015,10 +1955,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589253</v>
+        <v>589211</v>
       </c>
       <c r="R13" t="n">
-        <v>6931269</v>
+        <v>6931367</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2050,7 +1990,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2060,7 +2000,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2087,15 +2027,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125287628</v>
+        <v>125287933</v>
       </c>
       <c r="B14" t="n">
-        <v>80028</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80070</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2127,10 +2062,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589213</v>
+        <v>589253</v>
       </c>
       <c r="R14" t="n">
-        <v>6931355</v>
+        <v>6931269</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2162,7 +2097,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2172,7 +2107,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2187,12 +2122,12 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 12205-2025 artfynd.xlsx
+++ b/artfynd/A 12205-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125288594</v>
+        <v>125287248</v>
       </c>
       <c r="B2" t="n">
-        <v>57811</v>
+        <v>57651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589268</v>
+        <v>589263</v>
       </c>
       <c r="R2" t="n">
-        <v>6931468</v>
+        <v>6931366</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Satt bakom ett träd, flög iväg när jag försökte få den på video.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +794,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125287248</v>
+        <v>125288594</v>
       </c>
       <c r="B3" t="n">
-        <v>57651</v>
+        <v>57811</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,41 +817,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589263</v>
+        <v>589268</v>
       </c>
       <c r="R3" t="n">
-        <v>6931366</v>
+        <v>6931468</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Satt bakom ett träd, flög iväg när jag försökte få den på video.</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,12 +906,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>

--- a/artfynd/A 12205-2025 artfynd.xlsx
+++ b/artfynd/A 12205-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125287248</v>
+        <v>125288594</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>57811</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,41 +686,27 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -729,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589263</v>
+        <v>589268</v>
       </c>
       <c r="R2" t="n">
-        <v>6931366</v>
+        <v>6931468</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Satt bakom ett träd, flög iväg när jag försökte få den på video.</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -794,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125288594</v>
+        <v>125287248</v>
       </c>
       <c r="B3" t="n">
-        <v>57811</v>
+        <v>57651</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,27 +798,41 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -846,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589268</v>
+        <v>589263</v>
       </c>
       <c r="R3" t="n">
-        <v>6931468</v>
+        <v>6931366</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +876,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +886,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Satt bakom ett träd, flög iväg när jag försökte få den på video.</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,12 +906,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1038,7 +1038,7 @@
         <v>125288341</v>
       </c>
       <c r="B5" t="n">
-        <v>97202</v>
+        <v>97209</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125288104</v>
+        <v>125287941</v>
       </c>
       <c r="B6" t="n">
-        <v>56834</v>
+        <v>57811</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,27 +1153,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589218</v>
+        <v>589240</v>
       </c>
       <c r="R6" t="n">
-        <v>6931404</v>
+        <v>6931271</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,22 +1242,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125287941</v>
+        <v>125288104</v>
       </c>
       <c r="B7" t="n">
-        <v>57811</v>
+        <v>56834</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,27 +1265,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1294,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589240</v>
+        <v>589218</v>
       </c>
       <c r="R7" t="n">
-        <v>6931271</v>
+        <v>6931404</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,12 +1354,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1816,7 +1816,7 @@
         <v>125289593</v>
       </c>
       <c r="B12" t="n">
-        <v>91220</v>
+        <v>91227</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 12205-2025 artfynd.xlsx
+++ b/artfynd/A 12205-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125288594</v>
+        <v>125287248</v>
       </c>
       <c r="B2" t="n">
-        <v>57811</v>
+        <v>57651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,27 +686,41 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -715,10 +729,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589268</v>
+        <v>589263</v>
       </c>
       <c r="R2" t="n">
-        <v>6931468</v>
+        <v>6931366</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +764,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +774,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Satt bakom ett träd, flög iväg när jag försökte få den på video.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +794,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125287248</v>
+        <v>125288594</v>
       </c>
       <c r="B3" t="n">
-        <v>57651</v>
+        <v>57811</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -798,41 +817,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -841,10 +846,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589263</v>
+        <v>589268</v>
       </c>
       <c r="R3" t="n">
-        <v>6931366</v>
+        <v>6931468</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -876,7 +881,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -886,12 +891,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Satt bakom ett träd, flög iväg när jag försökte få den på video.</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,12 +906,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1478,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125287628</v>
+        <v>125288613</v>
       </c>
       <c r="B9" t="n">
-        <v>80070</v>
+        <v>56227</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,34 +1489,39 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589213</v>
+        <v>589274</v>
       </c>
       <c r="R9" t="n">
-        <v>6931355</v>
+        <v>6931451</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,7 +1553,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1563,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,7 +1590,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125288613</v>
+        <v>125289100</v>
       </c>
       <c r="B10" t="n">
         <v>56227</v>
@@ -1613,7 +1618,11 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>äldre spillning</t>
@@ -1625,10 +1634,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589274</v>
+        <v>589290</v>
       </c>
       <c r="R10" t="n">
-        <v>6931451</v>
+        <v>6931449</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1660,7 +1669,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1670,7 +1679,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1697,10 +1706,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125289100</v>
+        <v>125287628</v>
       </c>
       <c r="B11" t="n">
-        <v>56227</v>
+        <v>80070</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,43 +1717,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589290</v>
+        <v>589213</v>
       </c>
       <c r="R11" t="n">
-        <v>6931449</v>
+        <v>6931355</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 12205-2025 artfynd.xlsx
+++ b/artfynd/A 12205-2025 artfynd.xlsx
@@ -1038,7 +1038,7 @@
         <v>125288341</v>
       </c>
       <c r="B5" t="n">
-        <v>97209</v>
+        <v>97212</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1142,10 +1142,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125287941</v>
+        <v>125288104</v>
       </c>
       <c r="B6" t="n">
-        <v>57811</v>
+        <v>56834</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,27 +1153,27 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>102612</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589240</v>
+        <v>589218</v>
       </c>
       <c r="R6" t="n">
-        <v>6931271</v>
+        <v>6931404</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1217,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,22 +1242,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125288104</v>
+        <v>125287941</v>
       </c>
       <c r="B7" t="n">
-        <v>56834</v>
+        <v>57811</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,27 +1265,27 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102612</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1294,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589218</v>
+        <v>589240</v>
       </c>
       <c r="R7" t="n">
-        <v>6931404</v>
+        <v>6931271</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,7 +1329,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,12 +1354,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1709,7 +1709,7 @@
         <v>125287628</v>
       </c>
       <c r="B11" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1816,7 +1816,7 @@
         <v>125289593</v>
       </c>
       <c r="B12" t="n">
-        <v>91227</v>
+        <v>91228</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1923,7 +1923,7 @@
         <v>125288182</v>
       </c>
       <c r="B13" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2030,7 +2030,7 @@
         <v>125287933</v>
       </c>
       <c r="B14" t="n">
-        <v>80070</v>
+        <v>80071</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>

--- a/artfynd/A 12205-2025 artfynd.xlsx
+++ b/artfynd/A 12205-2025 artfynd.xlsx
@@ -1478,10 +1478,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125288613</v>
+        <v>125287628</v>
       </c>
       <c r="B9" t="n">
-        <v>56227</v>
+        <v>80071</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1489,39 +1489,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>206004</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589274</v>
+        <v>589213</v>
       </c>
       <c r="R9" t="n">
-        <v>6931451</v>
+        <v>6931355</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1553,7 +1548,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1563,7 +1558,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,7 +1585,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125289100</v>
+        <v>125288613</v>
       </c>
       <c r="B10" t="n">
         <v>56227</v>
@@ -1618,11 +1613,7 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>äldre spillning</t>
@@ -1634,10 +1625,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589290</v>
+        <v>589274</v>
       </c>
       <c r="R10" t="n">
-        <v>6931449</v>
+        <v>6931451</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1669,7 +1660,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1679,7 +1670,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1706,10 +1697,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125287628</v>
+        <v>125289100</v>
       </c>
       <c r="B11" t="n">
-        <v>80071</v>
+        <v>56227</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1717,34 +1708,43 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589213</v>
+        <v>589290</v>
       </c>
       <c r="R11" t="n">
-        <v>6931355</v>
+        <v>6931449</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD11" t="b">

--- a/artfynd/A 12205-2025 artfynd.xlsx
+++ b/artfynd/A 12205-2025 artfynd.xlsx
@@ -1369,7 +1369,7 @@
         <v>125288954</v>
       </c>
       <c r="B8" t="n">
-        <v>57648</v>
+        <v>57658</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 12205-2025 artfynd.xlsx
+++ b/artfynd/A 12205-2025 artfynd.xlsx
@@ -1369,7 +1369,7 @@
         <v>125288954</v>
       </c>
       <c r="B8" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 12205-2025 artfynd.xlsx
+++ b/artfynd/A 12205-2025 artfynd.xlsx
@@ -1369,7 +1369,7 @@
         <v>125288954</v>
       </c>
       <c r="B8" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 12205-2025 artfynd.xlsx
+++ b/artfynd/A 12205-2025 artfynd.xlsx
@@ -1369,7 +1369,7 @@
         <v>125288954</v>
       </c>
       <c r="B8" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 12205-2025 artfynd.xlsx
+++ b/artfynd/A 12205-2025 artfynd.xlsx
@@ -1369,7 +1369,7 @@
         <v>125288954</v>
       </c>
       <c r="B8" t="n">
-        <v>57669</v>
+        <v>57670</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 12205-2025 artfynd.xlsx
+++ b/artfynd/A 12205-2025 artfynd.xlsx
@@ -1369,7 +1369,7 @@
         <v>125288954</v>
       </c>
       <c r="B8" t="n">
-        <v>57670</v>
+        <v>57681</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 12205-2025 artfynd.xlsx
+++ b/artfynd/A 12205-2025 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>125289297</v>
       </c>
       <c r="B4" t="n">
-        <v>57651</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 12205-2025 artfynd.xlsx
+++ b/artfynd/A 12205-2025 artfynd.xlsx
@@ -921,7 +921,7 @@
         <v>125289297</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 12205-2025 artfynd.xlsx
+++ b/artfynd/A 12205-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125287248</v>
+        <v>125289593</v>
       </c>
       <c r="B2" t="n">
-        <v>57651</v>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,53 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>589263</v>
+        <v>589278</v>
       </c>
       <c r="R2" t="n">
-        <v>6931366</v>
+        <v>6931421</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -764,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -774,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Satt bakom ett träd, flög iväg när jag försökte få den på video.</t>
+          <t>13:16</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -806,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125288594</v>
+        <v>125287628</v>
       </c>
       <c r="B3" t="n">
-        <v>57811</v>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,39 +793,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>589268</v>
+        <v>589213</v>
       </c>
       <c r="R3" t="n">
-        <v>6931468</v>
+        <v>6931355</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -891,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -906,22 +877,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125289297</v>
+        <v>125287933</v>
       </c>
       <c r="B4" t="n">
-        <v>57741</v>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,39 +900,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>589294</v>
+        <v>589253</v>
       </c>
       <c r="R4" t="n">
-        <v>6931466</v>
+        <v>6931269</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,7 +959,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:06</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1003,12 +969,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:06</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Ringhack av tretåig hackspett på Tall</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1023,44 +984,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125288341</v>
+        <v>125288182</v>
       </c>
       <c r="B5" t="n">
-        <v>97212</v>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>589259</v>
+        <v>589211</v>
       </c>
       <c r="R5" t="n">
-        <v>6931398</v>
+        <v>6931367</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1105,7 +1066,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1115,7 +1076,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>12:13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,27 +1103,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125288104</v>
+        <v>125288954</v>
       </c>
       <c r="B6" t="n">
-        <v>56834</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102612</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1173,7 +1134,7 @@
       <c r="I6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1182,10 +1143,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>589218</v>
+        <v>589305</v>
       </c>
       <c r="R6" t="n">
-        <v>6931404</v>
+        <v>6931466</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1217,7 +1178,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1227,7 +1188,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:11</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1242,22 +1203,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>125287941</v>
+        <v>125287248</v>
       </c>
       <c r="B7" t="n">
-        <v>57811</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1265,27 +1226,41 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1294,10 +1269,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>589240</v>
+        <v>589263</v>
       </c>
       <c r="R7" t="n">
-        <v>6931271</v>
+        <v>6931366</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1329,7 +1304,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1339,7 +1314,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Satt bakom ett träd, flög iväg när jag försökte få den på video.</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1354,22 +1334,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125288954</v>
+        <v>125289297</v>
       </c>
       <c r="B8" t="n">
-        <v>57681</v>
+        <v>57953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1377,16 +1357,16 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1406,7 +1386,7 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>589305</v>
+        <v>589294</v>
       </c>
       <c r="R8" t="n">
         <v>6931466</v>
@@ -1441,7 +1421,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1451,7 +1431,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack av tretåig hackspett på Tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1466,57 +1451,62 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125287628</v>
+        <v>125288104</v>
       </c>
       <c r="B9" t="n">
-        <v>80071</v>
+        <v>57132</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>589213</v>
+        <v>589218</v>
       </c>
       <c r="R9" t="n">
-        <v>6931355</v>
+        <v>6931404</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1548,7 +1538,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1558,7 +1548,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1585,10 +1575,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125288613</v>
+        <v>125287941</v>
       </c>
       <c r="B10" t="n">
-        <v>56227</v>
+        <v>58114</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1596,27 +1586,27 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>206004</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1625,10 +1615,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>589274</v>
+        <v>589240</v>
       </c>
       <c r="R10" t="n">
-        <v>6931451</v>
+        <v>6931271</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1660,7 +1650,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1670,7 +1660,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1685,22 +1675,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125289100</v>
+        <v>125288594</v>
       </c>
       <c r="B11" t="n">
-        <v>56227</v>
+        <v>58114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1708,31 +1698,27 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>206004</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skogshare</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lepus timidus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1741,10 +1727,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>589290</v>
+        <v>589268</v>
       </c>
       <c r="R11" t="n">
-        <v>6931449</v>
+        <v>6931468</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1776,7 +1762,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1786,7 +1772,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1801,22 +1787,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Linnea Silverliv</t>
+          <t>Joel Helker-Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125289593</v>
+        <v>125288613</v>
       </c>
       <c r="B12" t="n">
-        <v>91228</v>
+        <v>56522</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1824,34 +1810,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1202</v>
+        <v>206004</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>589278</v>
+        <v>589274</v>
       </c>
       <c r="R12" t="n">
-        <v>6931421</v>
+        <v>6931451</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,7 +1874,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1884,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:16</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1920,10 +1911,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125288182</v>
+        <v>125289100</v>
       </c>
       <c r="B13" t="n">
-        <v>80071</v>
+        <v>56522</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1931,34 +1922,43 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>589211</v>
+        <v>589290</v>
       </c>
       <c r="R13" t="n">
-        <v>6931367</v>
+        <v>6931449</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:13</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2015,22 +2015,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Joel Helker-Nygren</t>
+          <t>Linnea Silverliv</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125287933</v>
+        <v>125290047</v>
       </c>
       <c r="B14" t="n">
-        <v>80071</v>
+        <v>56522</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2038,34 +2038,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>206004</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skogshare</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lepus timidus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Palamstjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>589253</v>
+        <v>589215</v>
       </c>
       <c r="R14" t="n">
-        <v>6931269</v>
+        <v>6931248</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2097,7 +2102,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2107,7 +2112,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>13:38</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2122,15 +2127,122 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Linnea Silverliv</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>125288341</v>
+      </c>
+      <c r="B15" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Palamstjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>589259</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6931398</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sundsvall</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Stöde</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-05-21</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>12:21</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
           <t>Joel Helker-Nygren</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
+      <c r="AX15" t="inlineStr">
         <is>
           <t>Joel Helker-Nygren</t>
         </is>
       </c>
-      <c r="AY14" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 12205-2025 artfynd.xlsx
+++ b/artfynd/A 12205-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AZ15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125289593</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125287628</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -993,6 +1008,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125287933</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1100,6 +1120,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125288182</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125288954</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1343,6 +1373,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125287248</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1460,6 +1495,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125289297</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1572,6 +1612,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125288104</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1684,6 +1729,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125287941</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1796,6 +1846,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125288594</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1908,6 +1963,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125288613</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2024,6 +2084,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125289100</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2136,6 +2201,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125290047</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2243,8 +2313,29 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125288341</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>